--- a/demos/beyond-health/BH-Wellness-Care-Gap-SMS.xlsx
+++ b/demos/beyond-health/BH-Wellness-Care-Gap-SMS.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -452,13 +452,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hi {patient}, this is {hospital}. We're reaching out about an important part of your membership care plan.
-Reply 1 to continue. Reply STOP to opt out.</t>
+          <t>Hi {patient}, this is {hospital}. We're reaching out about an important part of your membership care plan.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1 — Continue</t>
+          <t>yep this is me</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -470,45 +469,94 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Thanks. Our records show you may be due for your annual wellness visit or a recommended preventive screening.
-Would you like help scheduling with Beyond Health?
-Reply 1 if yes, please help me schedule.
-Reply 2 if I already scheduled or completed this.
-Reply 3 if not right now.</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1 — Yes, please help me schedule</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
+          <t>Before we continue, can you confirm that you are {patient}?</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Thank you.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>yeah that would be great, I've been meaning to book something</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Wonderful — a team member will reach out to help you schedule at a time that works for you.
-Keeping your wellness visit current helps us catch issues early and personalize your hormone, weight, and primary care plan.
-Reply HELP for help. Reply STOP to unsubscribe.
-Thank you for choosing Beyond Health.</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Our records show you may be due for your annual wellness visit or a recommended preventive screening. Would you like help scheduling with Beyond Health?</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Wonderful. A team member will reach out to help you schedule at a time that works for you.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Keeping your wellness visit current helps us catch issues early and personalize your care plan.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Reply HELP for help. Reply STOP to unsubscribe. Thank you for choosing Beyond Health.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
